--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117797408</v>
+        <v>117797284</v>
       </c>
       <c r="B2" t="n">
-        <v>78125</v>
+        <v>79098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567840</v>
+        <v>567876</v>
       </c>
       <c r="R2" t="n">
-        <v>6465034</v>
+        <v>6464968</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Faxén, Jonas Lindebring, Karin Wilhelmsson</t>
+          <t>Karin Wilhelmsson, Jonas Lindebring, Carina Faxén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117797284</v>
+        <v>117797408</v>
       </c>
       <c r="B3" t="n">
-        <v>79098</v>
+        <v>78125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567876</v>
+        <v>567840</v>
       </c>
       <c r="R3" t="n">
-        <v>6464968</v>
+        <v>6465034</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson, Jonas Lindebring, Carina Faxén</t>
+          <t>Carina Faxén, Jonas Lindebring, Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117797408</v>
+        <v>117797034</v>
       </c>
       <c r="B3" t="n">
-        <v>78125</v>
+        <v>57303</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567840</v>
+        <v>567854</v>
       </c>
       <c r="R3" t="n">
-        <v>6465034</v>
+        <v>6464981</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,17 +884,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Faxén, Jonas Lindebring, Karin Wilhelmsson</t>
+          <t>Karin Wilhelmsson, Jonas Lindebring, Carina Faxén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117797086</v>
+        <v>117797408</v>
       </c>
       <c r="B4" t="n">
-        <v>56499</v>
+        <v>78125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,35 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567892</v>
+        <v>567840</v>
       </c>
       <c r="R4" t="n">
-        <v>6465013</v>
+        <v>6465034</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117797257</v>
+        <v>117797086</v>
       </c>
       <c r="B5" t="n">
-        <v>5480</v>
+        <v>56499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,32 +1009,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567888</v>
+        <v>567892</v>
       </c>
       <c r="R5" t="n">
-        <v>6464980</v>
+        <v>6465013</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117797034</v>
+        <v>117797257</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>5480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,31 +1123,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567854</v>
+        <v>567888</v>
       </c>
       <c r="R6" t="n">
-        <v>6464981</v>
+        <v>6464980</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,6 +1196,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117797284</v>
+        <v>117797257</v>
       </c>
       <c r="B2" t="n">
-        <v>79098</v>
+        <v>5480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567876</v>
+        <v>567888</v>
       </c>
       <c r="R2" t="n">
-        <v>6464968</v>
+        <v>6464980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -784,7 +786,7 @@
         <v>117797034</v>
       </c>
       <c r="B3" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117797408</v>
+        <v>117797086</v>
       </c>
       <c r="B4" t="n">
-        <v>78125</v>
+        <v>56500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,30 +905,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567840</v>
+        <v>567892</v>
       </c>
       <c r="R4" t="n">
-        <v>6465034</v>
+        <v>6465013</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117797086</v>
+        <v>117797297</v>
       </c>
       <c r="B5" t="n">
-        <v>56499</v>
+        <v>5480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,35 +1015,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567892</v>
+        <v>567867</v>
       </c>
       <c r="R5" t="n">
-        <v>6465013</v>
+        <v>6464980</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117797257</v>
+        <v>117797284</v>
       </c>
       <c r="B6" t="n">
-        <v>5480</v>
+        <v>79100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,28 +1127,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567888</v>
+        <v>567876</v>
       </c>
       <c r="R6" t="n">
-        <v>6464980</v>
+        <v>6464968</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117797297</v>
+        <v>117797408</v>
       </c>
       <c r="B7" t="n">
-        <v>5480</v>
+        <v>78127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,28 +1233,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567867</v>
+        <v>567840</v>
       </c>
       <c r="R7" t="n">
-        <v>6464980</v>
+        <v>6465034</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117797284</v>
+        <v>117797408</v>
       </c>
       <c r="B6" t="n">
-        <v>79100</v>
+        <v>78127</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567876</v>
+        <v>567840</v>
       </c>
       <c r="R6" t="n">
-        <v>6464968</v>
+        <v>6465034</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117797408</v>
+        <v>117797284</v>
       </c>
       <c r="B7" t="n">
-        <v>78127</v>
+        <v>79100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567840</v>
+        <v>567876</v>
       </c>
       <c r="R7" t="n">
-        <v>6465034</v>
+        <v>6464968</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,6 +1321,116 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117798314</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Odensgöl, Odensgöl, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567849</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6465020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson, Jonas Lindebring, Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>117798314</v>
       </c>
       <c r="B8" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1341,11 +1341,6 @@
       <c r="E8" t="n">
         <v>100138</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>117798314</v>
       </c>
       <c r="B8" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,6 +1340,11 @@
       </c>
       <c r="E8" t="n">
         <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson, Jonas Lindebring, Carina Faxén</t>
+          <t>Carina Faxén, Jonas Lindebring, Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>117798314</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Faxén, Jonas Lindebring, Karin Wilhelmsson</t>
+          <t>Karin Wilhelmsson, Jonas Lindebring, Carina Faxén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>117798314</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 2034-2024 artfynd.xlsx
+++ b/artfynd/A 2034-2024 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>117798314</v>
       </c>
       <c r="B8" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
